--- a/public/abc2/material/gestion-reporte.xlsx
+++ b/public/abc2/material/gestion-reporte.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -410,9 +410,12 @@
         <v>Tarea</v>
       </c>
       <c r="D1" t="str">
+        <v>Prioridad</v>
+      </c>
+      <c r="E1" t="str">
         <v>Estado</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Vence</v>
       </c>
     </row>
@@ -427,10 +430,13 @@
         <v>Cerrar objetivo mensual</v>
       </c>
       <c r="D2" t="str">
-        <v>En curso</v>
+        <v>Alta</v>
       </c>
       <c r="E2" t="str">
-        <v>05/07</v>
+        <v>Pendiente</v>
+      </c>
+      <c r="F2" t="str">
+        <v>01/07</v>
       </c>
     </row>
     <row r="3">
@@ -444,15 +450,18 @@
         <v>Reducir tiempos de respuesta</v>
       </c>
       <c r="D3" t="str">
-        <v>Pendiente</v>
+        <v>Media</v>
       </c>
       <c r="E3" t="str">
-        <v>10/07</v>
+        <v>En curso</v>
+      </c>
+      <c r="F3" t="str">
+        <v>04/07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Admin</v>
+        <v>Administración</v>
       </c>
       <c r="B4" t="str">
         <v>S. Ruiz</v>
@@ -461,10 +470,13 @@
         <v>Conciliar caja</v>
       </c>
       <c r="D4" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E4" t="str">
         <v>Listo</v>
       </c>
-      <c r="E4" t="str">
-        <v>01/07</v>
+      <c r="F4" t="str">
+        <v>07/07</v>
       </c>
     </row>
     <row r="5">
@@ -478,15 +490,418 @@
         <v>Planificar capacitación</v>
       </c>
       <c r="D5" t="str">
+        <v>Alta</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Demorado</v>
+      </c>
+      <c r="F5" t="str">
+        <v>10/07</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="B6" t="str">
+        <v>C. Torres</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Campaña de redes</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Media</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Pendiente</v>
+      </c>
+      <c r="F6" t="str">
+        <v>13/07</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Logística</v>
+      </c>
+      <c r="B7" t="str">
+        <v>A. Vega</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Optimizar rutas de entrega</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E7" t="str">
         <v>En curso</v>
       </c>
-      <c r="E5" t="str">
+      <c r="F7" t="str">
+        <v>16/07</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Ventas</v>
+      </c>
+      <c r="B8" t="str">
+        <v>M. López</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Actualizar base de clientes</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Alta</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Listo</v>
+      </c>
+      <c r="F8" t="str">
+        <v>19/07</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Atención</v>
+      </c>
+      <c r="B9" t="str">
+        <v>J. Díaz</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Revisar proveedores</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Media</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Demorado</v>
+      </c>
+      <c r="F9" t="str">
+        <v>22/07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Administración</v>
+      </c>
+      <c r="B10" t="str">
+        <v>S. Ruiz</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Encuesta de satisfacción</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Pendiente</v>
+      </c>
+      <c r="F10" t="str">
+        <v>25/07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>RRHH</v>
+      </c>
+      <c r="B11" t="str">
+        <v>P. Gómez</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Informe de resultados</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Alta</v>
+      </c>
+      <c r="E11" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="F11" t="str">
+        <v>28/07</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="B12" t="str">
+        <v>C. Torres</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Cerrar objetivo mensual</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Media</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Listo</v>
+      </c>
+      <c r="F12" t="str">
+        <v>03/07</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Logística</v>
+      </c>
+      <c r="B13" t="str">
+        <v>A. Vega</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Reducir tiempos de respuesta</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Demorado</v>
+      </c>
+      <c r="F13" t="str">
+        <v>06/07</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Ventas</v>
+      </c>
+      <c r="B14" t="str">
+        <v>M. López</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Conciliar caja</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Alta</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Pendiente</v>
+      </c>
+      <c r="F14" t="str">
+        <v>09/07</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Atención</v>
+      </c>
+      <c r="B15" t="str">
+        <v>J. Díaz</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Planificar capacitación</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Media</v>
+      </c>
+      <c r="E15" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="F15" t="str">
+        <v>12/07</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Administración</v>
+      </c>
+      <c r="B16" t="str">
+        <v>S. Ruiz</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Campaña de redes</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Listo</v>
+      </c>
+      <c r="F16" t="str">
         <v>15/07</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>RRHH</v>
+      </c>
+      <c r="B17" t="str">
+        <v>P. Gómez</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Optimizar rutas de entrega</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Alta</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Demorado</v>
+      </c>
+      <c r="F17" t="str">
+        <v>18/07</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="B18" t="str">
+        <v>C. Torres</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Actualizar base de clientes</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Media</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Pendiente</v>
+      </c>
+      <c r="F18" t="str">
+        <v>21/07</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Logística</v>
+      </c>
+      <c r="B19" t="str">
+        <v>A. Vega</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Revisar proveedores</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E19" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="F19" t="str">
+        <v>24/07</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Ventas</v>
+      </c>
+      <c r="B20" t="str">
+        <v>M. López</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Encuesta de satisfacción</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Alta</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Listo</v>
+      </c>
+      <c r="F20" t="str">
+        <v>27/07</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Atención</v>
+      </c>
+      <c r="B21" t="str">
+        <v>J. Díaz</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Informe de resultados</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Media</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Demorado</v>
+      </c>
+      <c r="F21" t="str">
+        <v>02/07</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Administración</v>
+      </c>
+      <c r="B22" t="str">
+        <v>S. Ruiz</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Cerrar objetivo mensual</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Pendiente</v>
+      </c>
+      <c r="F22" t="str">
+        <v>05/07</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>RRHH</v>
+      </c>
+      <c r="B23" t="str">
+        <v>P. Gómez</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Reducir tiempos de respuesta</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Alta</v>
+      </c>
+      <c r="E23" t="str">
+        <v>En curso</v>
+      </c>
+      <c r="F23" t="str">
+        <v>08/07</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="B24" t="str">
+        <v>C. Torres</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Conciliar caja</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Media</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Listo</v>
+      </c>
+      <c r="F24" t="str">
+        <v>11/07</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Logística</v>
+      </c>
+      <c r="B25" t="str">
+        <v>A. Vega</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Planificar capacitación</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Baja</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Demorado</v>
+      </c>
+      <c r="F25" t="str">
+        <v>14/07</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F25"/>
   </ignoredErrors>
 </worksheet>
 </file>